--- a/file_upload_forms/024_signage_detail_collection_form--file_upload_forms.xlsx
+++ b/file_upload_forms/024_signage_detail_collection_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1112,34 +1112,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sign_type_choices</t>
+          <t>sign_color_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>directional_sign</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Directional Sign</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sign_type_choices</t>
+          <t>sign_color_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>directional_sign</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Directional Sign</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
@@ -1236,46 +1236,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sign_color_choices</t>
+          <t>project_approver_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sign_color_choices</t>
+          <t>project_approver_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -1287,44 +1287,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>john_doe</t>
+          <t>bob_johnson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>John Doe</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>project_approver_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>jane_smith</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jane Smith</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>project_approver_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bob_johnson</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>Bob Johnson</t>
         </is>
